--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1523"/>
+  <dimension ref="A1:C1524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17143,6 +17143,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1524" spans="1:3">
+      <c r="A1524" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B1524">
+        <v>108825</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1524"/>
+  <dimension ref="A1:C1525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17154,6 +17154,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1525" spans="1:3">
+      <c r="A1525" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B1525">
+        <v>107725</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1525"/>
+  <dimension ref="A1:C1526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17165,6 +17165,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1526" spans="1:3">
+      <c r="A1526" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B1526">
+        <v>108130</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1526"/>
+  <dimension ref="A1:C1527"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17176,6 +17176,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1527" spans="1:3">
+      <c r="A1527" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B1527">
+        <v>108810</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1527"/>
+  <dimension ref="A1:C1528"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17187,6 +17187,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1528" spans="1:3">
+      <c r="A1528" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1528">
+        <v>110200</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1528"/>
+  <dimension ref="A1:C1529"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17198,6 +17198,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1529" spans="1:3">
+      <c r="A1529" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1529">
+        <v>110800</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1529"/>
+  <dimension ref="A1:C1530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17209,6 +17209,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1530" spans="1:3">
+      <c r="A1530" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B1530">
+        <v>112700</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1530"/>
+  <dimension ref="A1:C1531"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17220,6 +17220,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1531" spans="1:3">
+      <c r="A1531" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B1531">
+        <v>112510</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1531"/>
+  <dimension ref="A1:C1532"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17231,6 +17231,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1532" spans="1:3">
+      <c r="A1532" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B1532">
+        <v>112100</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1532"/>
+  <dimension ref="A1:C1533"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17242,6 +17242,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1533" spans="1:3">
+      <c r="A1533" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B1533">
+        <v>112100</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1533"/>
+  <dimension ref="A1:C1534"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17253,6 +17253,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1534" spans="1:3">
+      <c r="A1534" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B1534">
+        <v>111180</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1534"/>
+  <dimension ref="A1:C1535"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17264,6 +17264,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1535" spans="1:3">
+      <c r="A1535" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B1535">
+        <v>111090</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1535"/>
+  <dimension ref="A1:C1536"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17275,6 +17275,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1536" spans="1:3">
+      <c r="A1536" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B1536">
+        <v>111380</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1536"/>
+  <dimension ref="A1:C1537"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17286,6 +17286,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1537" spans="1:3">
+      <c r="A1537" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B1537">
+        <v>111380</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1537"/>
+  <dimension ref="A1:C1538"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17297,6 +17297,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1538" spans="1:3">
+      <c r="A1538" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B1538">
+        <v>111380</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1538"/>
+  <dimension ref="A1:C1539"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17308,6 +17308,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1539" spans="1:3">
+      <c r="A1539" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B1539">
+        <v>111380</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1539"/>
+  <dimension ref="A1:C1540"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17319,6 +17319,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1540" spans="1:3">
+      <c r="A1540" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B1540">
+        <v>111380</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1540"/>
+  <dimension ref="A1:C1541"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17330,6 +17330,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1541" spans="1:3">
+      <c r="A1541" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B1541">
+        <v>111380</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1541"/>
+  <dimension ref="A1:C1542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17341,6 +17341,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1542" spans="1:3">
+      <c r="A1542" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B1542">
+        <v>112525</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1542"/>
+  <dimension ref="A1:C1543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17352,6 +17352,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1543" spans="1:3">
+      <c r="A1543" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B1543">
+        <v>111450</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1543"/>
+  <dimension ref="A1:C1544"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17363,6 +17363,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1544" spans="1:3">
+      <c r="A1544" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1544">
+        <v>111880</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1544"/>
+  <dimension ref="A1:C1545"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17374,6 +17374,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1545" spans="1:3">
+      <c r="A1545" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1545">
+        <v>111350</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1545"/>
+  <dimension ref="A1:C1546"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17385,6 +17385,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1546" spans="1:3">
+      <c r="A1546" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1546">
+        <v>111620</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1546"/>
+  <dimension ref="A1:C1547"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17396,6 +17396,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1547" spans="1:3">
+      <c r="A1547" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1547">
+        <v>110525</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1547"/>
+  <dimension ref="A1:C1548"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17407,6 +17407,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1548" spans="1:3">
+      <c r="A1548" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1548">
+        <v>110680</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1548"/>
+  <dimension ref="A1:C1549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17418,6 +17418,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1549" spans="1:3">
+      <c r="A1549" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1549">
+        <v>110690</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1549"/>
+  <dimension ref="A1:C1550"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17429,6 +17429,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1550" spans="1:3">
+      <c r="A1550" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1550">
+        <v>109930</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1550"/>
+  <dimension ref="A1:C1551"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17440,6 +17440,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1551" spans="1:3">
+      <c r="A1551" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B1551">
+        <v>110550</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1551"/>
+  <dimension ref="A1:C1552"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17451,6 +17451,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1552" spans="1:3">
+      <c r="A1552" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B1552">
+        <v>109680</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1552"/>
+  <dimension ref="A1:C1553"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17462,6 +17462,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1553" spans="1:3">
+      <c r="A1553" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B1553">
+        <v>108830</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1553"/>
+  <dimension ref="A1:C1554"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17473,6 +17473,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1554" spans="1:3">
+      <c r="A1554" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B1554">
+        <v>109650</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1554"/>
+  <dimension ref="A1:C1555"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17484,6 +17484,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1555" spans="1:3">
+      <c r="A1555" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B1555">
+        <v>110350</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1555"/>
+  <dimension ref="A1:C1556"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17495,6 +17495,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1556" spans="1:3">
+      <c r="A1556" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B1556">
+        <v>110950</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1556"/>
+  <dimension ref="A1:C1557"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17506,6 +17506,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1557" spans="1:3">
+      <c r="A1557" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B1557">
+        <v>110855</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/shmet/data/shmet_historical.xlsx
+++ b/LME/parser/shmet/data/shmet_historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1557"/>
+  <dimension ref="A1:C1558"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -17517,6 +17517,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1558" spans="1:3">
+      <c r="A1558" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B1558">
+        <v>110270</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
